--- a/Excel/Vertical/perbandingan_Jumlah Close.xlsx
+++ b/Excel/Vertical/perbandingan_Jumlah Close.xlsx
@@ -450,10 +450,10 @@
         <v>3</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>0.6206896551724138</v>
+        <v>0.7413793103448276</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -473,10 +473,10 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>0.8589211618257261</v>
+        <v>0.8962655601659751</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -496,10 +496,10 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>0.9643947100712106</v>
+        <v>0.9735503560528993</v>
       </c>
       <c r="G4" t="s">
         <v>12</v>
@@ -519,10 +519,10 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>0.9912038200552903</v>
+        <v>0.9937170143252073</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
@@ -542,10 +542,10 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>0.6515151515151515</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
@@ -565,10 +565,10 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F7">
-        <v>0.8255813953488372</v>
+        <v>0.8720930232558139</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -588,10 +588,10 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F8">
-        <v>0.9585342333654774</v>
+        <v>0.9681774349083896</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
@@ -611,10 +611,10 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F9">
-        <v>0.9898868287984589</v>
+        <v>0.9908499879605105</v>
       </c>
       <c r="G9" t="s">
         <v>12</v>
@@ -634,10 +634,10 @@
         <v>9</v>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>0.6271186440677966</v>
+        <v>0.6101694915254238</v>
       </c>
       <c r="G10" t="s">
         <v>12</v>
@@ -657,10 +657,10 @@
         <v>9</v>
       </c>
       <c r="E11">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>0.8401639344262295</v>
+        <v>0.8729508196721312</v>
       </c>
       <c r="G11" t="s">
         <v>12</v>
@@ -680,10 +680,10 @@
         <v>9</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>0.9653061224489796</v>
+        <v>0.9673469387755103</v>
       </c>
       <c r="G12" t="s">
         <v>12</v>
@@ -703,10 +703,10 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F13">
-        <v>0.9913243174279153</v>
+        <v>0.9920898188313345</v>
       </c>
       <c r="G13" t="s">
         <v>12</v>
@@ -726,10 +726,10 @@
         <v>10</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F14">
-        <v>0.6428571428571429</v>
+        <v>0.7571428571428571</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -749,10 +749,10 @@
         <v>10</v>
       </c>
       <c r="E15">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F15">
-        <v>0.8695652173913043</v>
+        <v>0.9057971014492754</v>
       </c>
       <c r="G15" t="s">
         <v>12</v>
@@ -772,10 +772,10 @@
         <v>10</v>
       </c>
       <c r="E16">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F16">
-        <v>0.9689387402933564</v>
+        <v>0.9784296807592753</v>
       </c>
       <c r="G16" t="s">
         <v>12</v>
@@ -795,10 +795,10 @@
         <v>10</v>
       </c>
       <c r="E17">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F17">
-        <v>0.9927745664739884</v>
+        <v>0.9948389760528489</v>
       </c>
       <c r="G17" t="s">
         <v>12</v>
@@ -818,10 +818,10 @@
         <v>11</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F18">
-        <v>0.7922077922077922</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="G18" t="s">
         <v>12</v>
@@ -841,10 +841,10 @@
         <v>11</v>
       </c>
       <c r="E19">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F19">
-        <v>0.9121621621621622</v>
+        <v>0.9459459459459459</v>
       </c>
       <c r="G19" t="s">
         <v>12</v>
@@ -864,10 +864,10 @@
         <v>11</v>
       </c>
       <c r="E20">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F20">
-        <v>0.979235880398671</v>
+        <v>0.9867109634551495</v>
       </c>
       <c r="G20" t="s">
         <v>12</v>
@@ -887,10 +887,10 @@
         <v>11</v>
       </c>
       <c r="E21">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F21">
-        <v>0.9949000407996736</v>
+        <v>0.9967360261117911</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>

--- a/Excel/Vertical/perbandingan_Jumlah Close.xlsx
+++ b/Excel/Vertical/perbandingan_Jumlah Close.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="14">
   <si>
     <t>Kombinasi</t>
   </si>
@@ -22,7 +22,7 @@
     <t>Ukuran</t>
   </si>
   <si>
-    <t>Nilai</t>
+    <t>value</t>
   </si>
   <si>
     <t>Map</t>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>Tetap</t>
+  </si>
+  <si>
+    <t>Naik</t>
   </si>
 </sst>
 </file>
@@ -449,6 +452,12 @@
       <c r="D2" t="s">
         <v>3</v>
       </c>
+      <c r="E2">
+        <v>58</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
       <c r="G2" t="s">
         <v>12</v>
       </c>
@@ -466,6 +475,12 @@
       <c r="D3" t="s">
         <v>3</v>
       </c>
+      <c r="E3">
+        <v>241</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
       <c r="G3" t="s">
         <v>12</v>
       </c>
@@ -483,6 +498,12 @@
       <c r="D4" t="s">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>983</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
       <c r="G4" t="s">
         <v>12</v>
       </c>
@@ -500,6 +521,12 @@
       <c r="D5" t="s">
         <v>3</v>
       </c>
+      <c r="E5">
+        <v>3979</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
       <c r="G5" t="s">
         <v>12</v>
       </c>
@@ -517,8 +544,14 @@
       <c r="D6" t="s">
         <v>8</v>
       </c>
+      <c r="E6">
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <v>0.696969696969697</v>
+      </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -534,8 +567,14 @@
       <c r="D7" t="s">
         <v>8</v>
       </c>
+      <c r="E7">
+        <v>45</v>
+      </c>
+      <c r="F7">
+        <v>0.8255813953488372</v>
+      </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -551,8 +590,14 @@
       <c r="D8" t="s">
         <v>8</v>
       </c>
+      <c r="E8">
+        <v>142</v>
+      </c>
+      <c r="F8">
+        <v>0.863066538090646</v>
+      </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -568,8 +613,14 @@
       <c r="D9" t="s">
         <v>8</v>
       </c>
+      <c r="E9">
+        <v>587</v>
+      </c>
+      <c r="F9">
+        <v>0.8586563929689381</v>
+      </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -585,8 +636,14 @@
       <c r="D10" t="s">
         <v>9</v>
       </c>
+      <c r="E10">
+        <v>35</v>
+      </c>
+      <c r="F10">
+        <v>0.4067796610169492</v>
+      </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -602,8 +659,14 @@
       <c r="D11" t="s">
         <v>9</v>
       </c>
+      <c r="E11">
+        <v>132</v>
+      </c>
+      <c r="F11">
+        <v>0.459016393442623</v>
+      </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -619,8 +682,14 @@
       <c r="D12" t="s">
         <v>9</v>
       </c>
+      <c r="E12">
+        <v>515</v>
+      </c>
+      <c r="F12">
+        <v>0.4744897959183674</v>
+      </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -636,8 +705,14 @@
       <c r="D13" t="s">
         <v>9</v>
       </c>
+      <c r="E13">
+        <v>2026</v>
+      </c>
+      <c r="F13">
+        <v>0.4830313855575402</v>
+      </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -653,8 +728,14 @@
       <c r="D14" t="s">
         <v>10</v>
       </c>
+      <c r="E14">
+        <v>25</v>
+      </c>
+      <c r="F14">
+        <v>0.6428571428571429</v>
+      </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -670,8 +751,14 @@
       <c r="D15" t="s">
         <v>10</v>
       </c>
+      <c r="E15">
+        <v>38</v>
+      </c>
+      <c r="F15">
+        <v>0.8623188405797102</v>
+      </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -687,8 +774,14 @@
       <c r="D16" t="s">
         <v>10</v>
       </c>
+      <c r="E16">
+        <v>39</v>
+      </c>
+      <c r="F16">
+        <v>0.9663503019844694</v>
+      </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -704,8 +797,14 @@
       <c r="D17" t="s">
         <v>10</v>
       </c>
+      <c r="E17">
+        <v>41</v>
+      </c>
+      <c r="F17">
+        <v>0.9915359207266722</v>
+      </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -721,8 +820,14 @@
       <c r="D18" t="s">
         <v>11</v>
       </c>
+      <c r="E18">
+        <v>58</v>
+      </c>
+      <c r="F18">
+        <v>0.2467532467532468</v>
+      </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -738,8 +843,14 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
+      <c r="E19">
+        <v>241</v>
+      </c>
+      <c r="F19">
+        <v>0.1858108108108108</v>
+      </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -755,8 +866,14 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
+      <c r="E20">
+        <v>983</v>
+      </c>
+      <c r="F20">
+        <v>0.1835548172757475</v>
+      </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -772,8 +889,14 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
+      <c r="E21">
+        <v>3979</v>
+      </c>
+      <c r="F21">
+        <v>0.1882904936760506</v>
+      </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Vertical/perbandingan_Jumlah Close.xlsx
+++ b/Excel/Vertical/perbandingan_Jumlah Close.xlsx
@@ -568,10 +568,10 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F7">
-        <v>0.8255813953488372</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -591,10 +591,10 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="F8">
-        <v>0.863066538090646</v>
+        <v>0.9151398264223722</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -614,10 +614,10 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>587</v>
+        <v>196</v>
       </c>
       <c r="F9">
-        <v>0.8586563929689381</v>
+        <v>0.9528052010594751</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
